--- a/احصاء_المنخرطين.xlsx
+++ b/احصاء_المنخرطين.xlsx
@@ -49,24 +49,6 @@
     <t>الجملة</t>
   </si>
   <si>
-    <t>HNBL</t>
-  </si>
-  <si>
-    <t>YSMN</t>
-  </si>
-  <si>
-    <t>KRWN</t>
-  </si>
-  <si>
-    <t>ASHQ</t>
-  </si>
-  <si>
-    <t>BLQS</t>
-  </si>
-  <si>
-    <t>MRYM</t>
-  </si>
-  <si>
     <t>حنبعل</t>
   </si>
   <si>
@@ -92,6 +74,24 @@
   </si>
   <si>
     <t>2024-2025</t>
+  </si>
+  <si>
+    <t>RCHT</t>
+  </si>
+  <si>
+    <t>ZHRT</t>
+  </si>
+  <si>
+    <t>CHBL</t>
+  </si>
+  <si>
+    <t>CHFA</t>
+  </si>
+  <si>
+    <t>LILT</t>
+  </si>
+  <si>
+    <t>JWLA</t>
   </si>
 </sst>
 </file>
@@ -476,13 +476,13 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>17</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
       </c>
       <c r="D2" s="1">
         <v>44927</v>
@@ -511,13 +511,13 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D3" s="1">
         <v>45292</v>
@@ -546,13 +546,13 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D4" s="1">
         <v>45658</v>
@@ -581,13 +581,13 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D5" s="1">
         <v>44927</v>
@@ -616,13 +616,13 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
       </c>
       <c r="D6" s="1">
         <v>45292</v>
@@ -651,13 +651,13 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D7" s="1">
         <v>45658</v>
@@ -686,13 +686,13 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
         <v>13</v>
       </c>
-      <c r="B8" t="s">
-        <v>19</v>
-      </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D8" s="1">
         <v>44927</v>
@@ -721,13 +721,13 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
         <v>13</v>
       </c>
-      <c r="B9" t="s">
-        <v>19</v>
-      </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D9" s="1">
         <v>45292</v>
@@ -756,13 +756,13 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
         <v>13</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>19</v>
-      </c>
-      <c r="C10" t="s">
-        <v>25</v>
       </c>
       <c r="D10" s="1">
         <v>45658</v>
@@ -791,13 +791,13 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
         <v>14</v>
       </c>
-      <c r="B11" t="s">
-        <v>20</v>
-      </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D11" s="1">
         <v>44927</v>
@@ -826,13 +826,13 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" t="s">
         <v>14</v>
       </c>
-      <c r="B12" t="s">
-        <v>20</v>
-      </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D12" s="1">
         <v>45292</v>
@@ -861,13 +861,13 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
         <v>14</v>
       </c>
-      <c r="B13" t="s">
-        <v>20</v>
-      </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D13" s="1">
         <v>45658</v>
@@ -896,13 +896,13 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" t="s">
         <v>15</v>
       </c>
-      <c r="B14" t="s">
-        <v>21</v>
-      </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D14" s="1">
         <v>44927</v>
@@ -931,13 +931,13 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s">
         <v>15</v>
       </c>
-      <c r="B15" t="s">
-        <v>21</v>
-      </c>
       <c r="C15" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D15" s="1">
         <v>45292</v>
@@ -966,13 +966,13 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" t="s">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
-        <v>21</v>
-      </c>
       <c r="C16" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D16" s="1">
         <v>45658</v>
@@ -1001,13 +1001,13 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" t="s">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
-        <v>22</v>
-      </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D17" s="1">
         <v>44927</v>
@@ -1036,13 +1036,13 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" t="s">
         <v>16</v>
       </c>
-      <c r="B18" t="s">
-        <v>22</v>
-      </c>
       <c r="C18" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D18" s="1">
         <v>45292</v>
@@ -1071,13 +1071,13 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" t="s">
         <v>16</v>
       </c>
-      <c r="B19" t="s">
-        <v>22</v>
-      </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D19" s="1">
         <v>45658</v>
